--- a/data/imdb_top250.xlsx
+++ b/data/imdb_top250.xlsx
@@ -4248,15 +4248,15 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Barry Lyndon</t>
+          <t>Warrior</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1975</v>
+        <v>2011</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>3h 5m</t>
+          <t>2h 20m</t>
         </is>
       </c>
       <c r="E183" t="n">
@@ -4269,15 +4269,15 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Warrior</t>
+          <t>Barry Lyndon</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>2011</v>
+        <v>1975</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2h 20m</t>
+          <t>3h 5m</t>
         </is>
       </c>
       <c r="E184" t="n">
